--- a/composition-eu-parent/ig/StructureDefinition-fr-performer-event-extension.xlsx
+++ b/composition-eu-parent/ig/StructureDefinition-fr-performer-event-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:41:40+00:00</t>
+    <t>2026-10-02T12:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/composition-eu-parent/ig/StructureDefinition-fr-performer-event-extension.xlsx
+++ b/composition-eu-parent/ig/StructureDefinition-fr-performer-event-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:54:07+00:00</t>
+    <t>2026-10-02T13:08:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/composition-eu-parent/ig/StructureDefinition-fr-performer-event-extension.xlsx
+++ b/composition-eu-parent/ig/StructureDefinition-fr-performer-event-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:08:18+00:00</t>
+    <t>2026-10-02T13:54:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
